--- a/Year_1.xlsx
+++ b/Year_1.xlsx
@@ -10,21 +10,25 @@
     <sheet name="NO_Variable_Pool_Number" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="NO_Variable_Recruitment_Amount" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="NO_Variable_Depth_cm" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="pNO_Variable_Julian_Day" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="pNO_Variable_Pool_Number" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="pNO_Variable_Recruitment_Amount" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="pNO_Variable_Depth_cm" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Ests_Overall" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Ests_Overall_sd" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="overall_pvalues" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="separate_values" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="overall_clusdiff_pvalues" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="NO_Variable_Temp_Reg" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NO_Variable_O2_Reg" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="pNO_Variable_Julian_Day" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="pNO_Variable_Pool_Number" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="pNO_Variable_Recruitment_Amount" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="pNO_Variable_Depth_cm" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="pNO_Variable_Temp_Reg" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="pNO_Variable_O2_Reg" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Ests_Overall" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Ests_Overall_sd" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="overall_pvalues" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="separate_clus_diff_pvalues" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="overall_clusdiff_pvalues" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -56,6 +60,9 @@
     <t xml:space="preserve">Springtail</t>
   </si>
   <si>
+    <t xml:space="preserve">varname</t>
+  </si>
+  <si>
     <t xml:space="preserve">separate.cluster.pvalues</t>
   </si>
   <si>
@@ -65,13 +72,37 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">Julian_Day</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pool_Number</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
+    <t xml:space="preserve">Recruitment_Amount</t>
+  </si>
+  <si>
     <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depth_cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temp_Reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O2_Reg</t>
   </si>
   <si>
     <t xml:space="preserve">overall.cluster.pvalues</t>
@@ -446,28 +477,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.353018026788146</v>
+        <v>0.271628564690276</v>
       </c>
       <c r="D2" t="n">
-        <v>0.583887712430907</v>
+        <v>0.587346141779866</v>
       </c>
       <c r="E2" t="n">
-        <v>0.529801926854877</v>
+        <v>0.422460867089186</v>
       </c>
       <c r="F2" t="n">
-        <v>0.43173894061645</v>
+        <v>0.216455808932126</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3777940095122</v>
+        <v>0.475621847996038</v>
       </c>
       <c r="H2" t="n">
-        <v>0.289361804341087</v>
+        <v>0.319020826721476</v>
       </c>
       <c r="I2" t="n">
-        <v>0.377470168134892</v>
+        <v>0.323329390963797</v>
       </c>
       <c r="J2" t="n">
-        <v>0.159760794268982</v>
+        <v>0.140145844826601</v>
       </c>
     </row>
     <row r="3">
@@ -475,31 +506,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.353018026788146</v>
+        <v>0.271628564690276</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.326883841861758</v>
+        <v>0.310968975701354</v>
       </c>
       <c r="E3" t="n">
-        <v>0.520128160217614</v>
+        <v>0.484477249532928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.670208151024212</v>
+        <v>0.691035595630105</v>
       </c>
       <c r="G3" t="n">
-        <v>0.181006928262324</v>
+        <v>0.181723935429283</v>
       </c>
       <c r="H3" t="n">
-        <v>0.557106663646723</v>
+        <v>0.538170063457673</v>
       </c>
       <c r="I3" t="n">
-        <v>0.530918013947276</v>
+        <v>0.355348003135413</v>
       </c>
       <c r="J3" t="n">
-        <v>0.598038349685784</v>
+        <v>0.673447711989145</v>
       </c>
     </row>
     <row r="4">
@@ -507,31 +538,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.583887712430907</v>
+        <v>0.587346141779866</v>
       </c>
       <c r="C4" t="n">
-        <v>0.326883841861758</v>
+        <v>0.310968975701354</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.499153955473125</v>
+        <v>0.446941298204121</v>
       </c>
       <c r="F4" t="n">
-        <v>0.437542449019838</v>
+        <v>0.241202495800016</v>
       </c>
       <c r="G4" t="n">
-        <v>0.631368232528401</v>
+        <v>0.651294080801922</v>
       </c>
       <c r="H4" t="n">
-        <v>0.288660158585583</v>
+        <v>0.328145219201781</v>
       </c>
       <c r="I4" t="n">
-        <v>0.370578607555576</v>
+        <v>0.364622172163859</v>
       </c>
       <c r="J4" t="n">
-        <v>0.161378064753913</v>
+        <v>0.160000621821541</v>
       </c>
     </row>
     <row r="5">
@@ -539,31 +570,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.529801926854877</v>
+        <v>0.422460867089186</v>
       </c>
       <c r="C5" t="n">
-        <v>0.520128160217614</v>
+        <v>0.484477249532928</v>
       </c>
       <c r="D5" t="n">
-        <v>0.499153955473125</v>
+        <v>0.446941298204121</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.756117742109566</v>
+        <v>0.560873891333905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.274358439538719</v>
+        <v>0.259553462299295</v>
       </c>
       <c r="H5" t="n">
-        <v>0.448438086651296</v>
+        <v>0.599026125411063</v>
       </c>
       <c r="I5" t="n">
-        <v>0.746574144136777</v>
+        <v>0.409558919041149</v>
       </c>
       <c r="J5" t="n">
-        <v>0.375589447728166</v>
+        <v>0.365436229235084</v>
       </c>
     </row>
     <row r="6">
@@ -571,31 +602,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.43173894061645</v>
+        <v>0.216455808932126</v>
       </c>
       <c r="C6" t="n">
-        <v>0.670208151024212</v>
+        <v>0.691035595630105</v>
       </c>
       <c r="D6" t="n">
-        <v>0.437542449019838</v>
+        <v>0.241202495800016</v>
       </c>
       <c r="E6" t="n">
-        <v>0.756117742109566</v>
+        <v>0.560873891333905</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.260180985718664</v>
+        <v>0.110037636609711</v>
       </c>
       <c r="H6" t="n">
-        <v>0.45736032013358</v>
+        <v>0.522908530364963</v>
       </c>
       <c r="I6" t="n">
-        <v>0.679448426140119</v>
+        <v>0.282806283846453</v>
       </c>
       <c r="J6" t="n">
-        <v>0.418323012380277</v>
+        <v>0.566222689316587</v>
       </c>
     </row>
     <row r="7">
@@ -603,31 +634,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3777940095122</v>
+        <v>0.475621847996038</v>
       </c>
       <c r="C7" t="n">
-        <v>0.181006928262324</v>
+        <v>0.181723935429283</v>
       </c>
       <c r="D7" t="n">
-        <v>0.631368232528401</v>
+        <v>0.651294080801922</v>
       </c>
       <c r="E7" t="n">
-        <v>0.274358439538719</v>
+        <v>0.259553462299295</v>
       </c>
       <c r="F7" t="n">
-        <v>0.260180985718664</v>
+        <v>0.110037636609711</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.141538860409284</v>
+        <v>0.182388051787716</v>
       </c>
       <c r="I7" t="n">
-        <v>0.189232809946896</v>
+        <v>0.238938395371178</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0432233527835648</v>
+        <v>0.0447746836548351</v>
       </c>
     </row>
     <row r="8">
@@ -635,31 +666,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.289361804341087</v>
+        <v>0.319020826721476</v>
       </c>
       <c r="C8" t="n">
-        <v>0.557106663646723</v>
+        <v>0.538170063457673</v>
       </c>
       <c r="D8" t="n">
-        <v>0.288660158585583</v>
+        <v>0.328145219201781</v>
       </c>
       <c r="E8" t="n">
-        <v>0.448438086651296</v>
+        <v>0.599026125411063</v>
       </c>
       <c r="F8" t="n">
-        <v>0.45736032013358</v>
+        <v>0.522908530364963</v>
       </c>
       <c r="G8" t="n">
-        <v>0.141538860409284</v>
+        <v>0.182388051787716</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.52935827212535</v>
+        <v>0.641204162432454</v>
       </c>
       <c r="J8" t="n">
-        <v>0.710774352162202</v>
+        <v>0.700938844130384</v>
       </c>
     </row>
     <row r="9">
@@ -667,31 +698,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.377470168134892</v>
+        <v>0.323329390963797</v>
       </c>
       <c r="C9" t="n">
-        <v>0.530918013947276</v>
+        <v>0.355348003135413</v>
       </c>
       <c r="D9" t="n">
-        <v>0.370578607555576</v>
+        <v>0.364622172163859</v>
       </c>
       <c r="E9" t="n">
-        <v>0.746574144136777</v>
+        <v>0.409558919041149</v>
       </c>
       <c r="F9" t="n">
-        <v>0.679448426140119</v>
+        <v>0.282806283846453</v>
       </c>
       <c r="G9" t="n">
-        <v>0.189232809946896</v>
+        <v>0.238938395371178</v>
       </c>
       <c r="H9" t="n">
-        <v>0.52935827212535</v>
+        <v>0.641204162432454</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.491161680358857</v>
+        <v>0.550957779380891</v>
       </c>
     </row>
     <row r="10">
@@ -699,28 +730,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.159760794268982</v>
+        <v>0.140145844826601</v>
       </c>
       <c r="C10" t="n">
-        <v>0.598038349685784</v>
+        <v>0.673447711989145</v>
       </c>
       <c r="D10" t="n">
-        <v>0.161378064753913</v>
+        <v>0.160000621821541</v>
       </c>
       <c r="E10" t="n">
-        <v>0.375589447728166</v>
+        <v>0.365436229235084</v>
       </c>
       <c r="F10" t="n">
-        <v>0.418323012380277</v>
+        <v>0.566222689316587</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0432233527835648</v>
+        <v>0.0447746836548351</v>
       </c>
       <c r="H10" t="n">
-        <v>0.710774352162202</v>
+        <v>0.700938844130384</v>
       </c>
       <c r="I10" t="n">
-        <v>0.491161680358857</v>
+        <v>0.550957779380891</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -774,31 +805,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.132414480793405</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.222756461200642</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.158842494249596</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.215339802195415</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.241789921402908</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.327701602925033</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.109691431483645</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.159276419930577</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -806,31 +837,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.132414480793405</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.171220937651192</v>
+        <v>0.002</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0868393843558947</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0821059667928247</v>
+        <v>0.007</v>
       </c>
       <c r="G3" t="n">
-        <v>0.175473068828273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.19550157793091</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.078737079631065</v>
+        <v>0.001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.078878331572566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -838,31 +869,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.222756461200642</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.171220937651192</v>
+        <v>0.002</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.171446054626189</v>
+        <v>0.002</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0592153117254298</v>
+        <v>0.003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0469226949049379</v>
+        <v>0.075</v>
       </c>
       <c r="H4" t="n">
-        <v>0.15523677735047</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.200178105045474</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.313695509006017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -870,31 +901,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.158842494249596</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0868393843558947</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.171446054626189</v>
+        <v>0.002</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0898622554125805</v>
+        <v>0.062</v>
       </c>
       <c r="G5" t="n">
-        <v>0.130072144781907</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.133091957930141</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.148240940917721</v>
+        <v>0.003</v>
       </c>
       <c r="J5" t="n">
-        <v>0.19777994867729</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="6">
@@ -902,31 +933,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.215339802195415</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0821059667928247</v>
+        <v>0.007</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0592153117254298</v>
+        <v>0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0898622554125805</v>
+        <v>0.062</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.190414540311136</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.220593173646863</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.178088745470977</v>
+        <v>0.042</v>
       </c>
       <c r="J6" t="n">
-        <v>0.124895707526494</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="7">
@@ -934,31 +965,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.241789921402908</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.175473068828273</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0469226949049379</v>
+        <v>0.075</v>
       </c>
       <c r="E7" t="n">
-        <v>0.130072144781907</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.190414540311136</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.287509363422776</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0760916658126684</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.201452164182754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -966,31 +997,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.327701602925033</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.19550157793091</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.15523677735047</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.133091957930141</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.220593173646863</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.287509363422776</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.203487351468678</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.273864425755095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -998,31 +1029,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.109691431483645</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.078737079631065</v>
+        <v>0.001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.200178105045474</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.148240940917721</v>
+        <v>0.003</v>
       </c>
       <c r="F9" t="n">
-        <v>0.178088745470977</v>
+        <v>0.042</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0760916658126684</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.203487351468678</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.190011776243111</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="10">
@@ -1030,31 +1061,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.159276419930577</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.078878331572566</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.313695509006017</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.19777994867729</v>
+        <v>0.005</v>
       </c>
       <c r="F10" t="n">
-        <v>0.124895707526494</v>
+        <v>0.075</v>
       </c>
       <c r="G10" t="n">
-        <v>0.201452164182754</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.273864425755095</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.190011776243111</v>
+        <v>0.023</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1146,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1178,13 +1209,13 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.009</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1204,25 +1235,25 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.009</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1236,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -1251,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="7">
@@ -1271,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1306,10 +1337,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1318,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1338,22 +1369,22 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="10">
@@ -1373,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1382,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1404,53 +1435,318 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.997</v>
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1470,21 +1766,1123 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.218290587710853</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.253234790882149</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.274037919425664</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.197620834042312</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.188810070994377</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.435869075697923</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.263291248137549</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.162013718433846</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.218290587710853</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.46462947954745</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.510634868616652</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.712511824216855</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.32691106550918</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.358094740667813</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.429186405184162</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.626519758591638</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.253234790882149</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.46462947954745</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.507803048674806</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.356862844299435</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.665173892819614</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.209907627315916</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.316998954305156</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.352933520285204</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.274037919425664</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.510634868616652</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.507803048674806</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.591348766939304</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.377775452788235</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.419673528110705</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4242619708271</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.47293478564015</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.197620834042312</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.712511824216855</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.356862844299435</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.591348766939304</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.278817186470709</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.375668668335214</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.392765481580625</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.629515560916324</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.188810070994377</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.32691106550918</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.665173892819614</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.377775452788235</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.278817186470709</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.139908915274508</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.196363686100468</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.198700554775093</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.435869075697923</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.358094740667813</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.209907627315916</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.419673528110705</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.375668668335214</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.139908915274508</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.442916055618727</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.390988889601417</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.263291248137549</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.429186405184162</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.316998954305156</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4242619708271</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.392765481580625</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.196363686100468</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.442916055618727</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.498382273048229</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.162013718433846</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.626519758591638</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.352933520285204</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.47293478564015</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.629515560916324</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.198700554775093</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.390988889601417</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.498382273048229</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0897792968566573</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.173769350106806</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0794221273389663</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0949423934866581</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.154452831057819</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.272189097366092</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0899785986487135</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.110572460536983</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0897792968566573</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.172986010094353</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0544691856393853</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0810180049777265</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.188915432407082</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.154623768710872</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.162074610989131</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0865341340586373</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.173769350106806</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.172986010094353</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0803031555035987</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.12900617078048</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0956996732980026</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0863816053584775</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.16774655870195</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.228037987924984</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0794221273389663</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0544691856393853</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0803031555035987</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.097365793195596</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.128319155689219</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.188859305109457</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0685537324715852</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.13858986862061</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0949423934866581</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0810180049777265</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.12900617078048</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.097365793195596</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.216869771226716</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.176345162436878</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.150683390413619</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.087776042857739</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.154452831057819</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.188915432407082</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0956996732980026</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.128319155689219</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.216869771226716</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.12729550855739</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0941131229362895</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.176714513459216</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.272189097366092</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.154623768710872</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0863816053584775</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.188859305109457</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.176345162436878</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.12729550855739</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.237686298177353</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.258636690031212</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0899785986487135</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.162074610989131</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.16774655870195</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0685537324715852</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.150683390413619</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0941131229362895</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.237686298177353</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.154178702121655</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.110572460536983</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0865341340586373</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.228037987924984</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.13858986862061</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.087776042857739</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.176714513459216</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.258636690031212</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.154178702121655</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>12</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.981</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.983</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.983</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
     </row>
   </sheetData>
@@ -1538,28 +2936,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0969436171673102</v>
+        <v>0.085726529081824</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0782783790586459</v>
+        <v>0.081994750656168</v>
       </c>
       <c r="E2" t="n">
-        <v>0.154906731549067</v>
+        <v>0.195840904502322</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0437956204379562</v>
+        <v>0.041994750656168</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0505473083599367</v>
+        <v>0.0450811704092544</v>
       </c>
       <c r="H2" t="n">
-        <v>0.990196078431373</v>
+        <v>0.991279069767442</v>
       </c>
       <c r="I2" t="n">
-        <v>0.197786672945609</v>
+        <v>0.206036745406824</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0523244050861438</v>
+        <v>0.052747438828211</v>
       </c>
     </row>
     <row r="3">
@@ -1567,31 +2965,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0969436171673102</v>
+        <v>0.085726529081824</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.675134632193306</v>
+        <v>0.70600583090379</v>
       </c>
       <c r="E3" t="n">
-        <v>0.632711002089579</v>
+        <v>0.427562233684683</v>
       </c>
       <c r="F3" t="n">
-        <v>0.631478227588247</v>
+        <v>0.58984892658362</v>
       </c>
       <c r="G3" t="n">
-        <v>0.397923888167463</v>
+        <v>0.318954036641111</v>
       </c>
       <c r="H3" t="n">
-        <v>0.098491133984256</v>
+        <v>0.0902434063326327</v>
       </c>
       <c r="I3" t="n">
-        <v>0.555033893387492</v>
+        <v>0.669946550048591</v>
       </c>
       <c r="J3" t="n">
-        <v>0.630150264911862</v>
+        <v>0.545346249098718</v>
       </c>
     </row>
     <row r="4">
@@ -1599,31 +2997,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0782783790586459</v>
+        <v>0.081994750656168</v>
       </c>
       <c r="C4" t="n">
-        <v>0.675134632193306</v>
+        <v>0.70600583090379</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.650383141762452</v>
+        <v>0.630769230769231</v>
       </c>
       <c r="F4" t="n">
-        <v>0.544387380777696</v>
+        <v>0.427272727272727</v>
       </c>
       <c r="G4" t="n">
-        <v>0.528701140802442</v>
+        <v>0.539012345679012</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0773749154834348</v>
+        <v>0.0850581395348837</v>
       </c>
       <c r="I4" t="n">
-        <v>0.681868743047831</v>
+        <v>0.618333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>0.675612087346519</v>
+        <v>0.55752688172043</v>
       </c>
     </row>
     <row r="5">
@@ -1631,31 +3029,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.154906731549067</v>
+        <v>0.195840904502322</v>
       </c>
       <c r="C5" t="n">
-        <v>0.632711002089579</v>
+        <v>0.427562233684683</v>
       </c>
       <c r="D5" t="n">
-        <v>0.650383141762452</v>
+        <v>0.630769230769231</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.76063829787234</v>
+        <v>0.506993006993007</v>
       </c>
       <c r="G5" t="n">
-        <v>0.510398432941569</v>
+        <v>0.561016144349478</v>
       </c>
       <c r="H5" t="n">
-        <v>0.154003267973856</v>
+        <v>0.198904293381038</v>
       </c>
       <c r="I5" t="n">
-        <v>0.508960573476703</v>
+        <v>0.46474358974359</v>
       </c>
       <c r="J5" t="n">
-        <v>0.717069414830609</v>
+        <v>0.507237386269644</v>
       </c>
     </row>
     <row r="6">
@@ -1663,31 +3061,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0437956204379562</v>
+        <v>0.041994750656168</v>
       </c>
       <c r="C6" t="n">
-        <v>0.631478227588247</v>
+        <v>0.58984892658362</v>
       </c>
       <c r="D6" t="n">
-        <v>0.544387380777696</v>
+        <v>0.427272727272727</v>
       </c>
       <c r="E6" t="n">
-        <v>0.76063829787234</v>
+        <v>0.506993006993007</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.609870552744569</v>
+        <v>0.312289562289562</v>
       </c>
       <c r="H6" t="n">
-        <v>0.045343137254902</v>
+        <v>0.0465116279069767</v>
       </c>
       <c r="I6" t="n">
-        <v>0.363074811256005</v>
+        <v>0.390151515151515</v>
       </c>
       <c r="J6" t="n">
-        <v>0.640702263757202</v>
+        <v>0.678641251221896</v>
       </c>
     </row>
     <row r="7">
@@ -1695,31 +3093,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0505473083599367</v>
+        <v>0.0450811704092544</v>
       </c>
       <c r="C7" t="n">
-        <v>0.397923888167463</v>
+        <v>0.318954036641111</v>
       </c>
       <c r="D7" t="n">
-        <v>0.528701140802442</v>
+        <v>0.539012345679012</v>
       </c>
       <c r="E7" t="n">
-        <v>0.510398432941569</v>
+        <v>0.561016144349478</v>
       </c>
       <c r="F7" t="n">
-        <v>0.609870552744569</v>
+        <v>0.312289562289562</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0496438447847256</v>
+        <v>0.0481445592879701</v>
       </c>
       <c r="I7" t="n">
-        <v>0.365341335333833</v>
+        <v>0.367283950617284</v>
       </c>
       <c r="J7" t="n">
-        <v>0.424532572375503</v>
+        <v>0.353942652329749</v>
       </c>
     </row>
     <row r="8">
@@ -1727,31 +3125,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.990196078431373</v>
+        <v>0.991279069767442</v>
       </c>
       <c r="C8" t="n">
-        <v>0.098491133984256</v>
+        <v>0.0902434063326327</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0773749154834348</v>
+        <v>0.0850581395348837</v>
       </c>
       <c r="E8" t="n">
-        <v>0.154003267973856</v>
+        <v>0.198904293381038</v>
       </c>
       <c r="F8" t="n">
-        <v>0.045343137254902</v>
+        <v>0.0465116279069767</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0496438447847256</v>
+        <v>0.0481445592879701</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.201731499051233</v>
+        <v>0.21172480620155</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0538719219030896</v>
+        <v>0.0572643160790198</v>
       </c>
     </row>
     <row r="9">
@@ -1759,31 +3157,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.197786672945609</v>
+        <v>0.206036745406824</v>
       </c>
       <c r="C9" t="n">
-        <v>0.555033893387492</v>
+        <v>0.669946550048591</v>
       </c>
       <c r="D9" t="n">
-        <v>0.681868743047831</v>
+        <v>0.618333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>0.508960573476703</v>
+        <v>0.46474358974359</v>
       </c>
       <c r="F9" t="n">
-        <v>0.363074811256005</v>
+        <v>0.390151515151515</v>
       </c>
       <c r="G9" t="n">
-        <v>0.365341335333833</v>
+        <v>0.367283950617284</v>
       </c>
       <c r="H9" t="n">
-        <v>0.201731499051233</v>
+        <v>0.21172480620155</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.560561249054268</v>
+        <v>0.508064516129032</v>
       </c>
     </row>
     <row r="10">
@@ -1791,28 +3189,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0523244050861438</v>
+        <v>0.052747438828211</v>
       </c>
       <c r="C10" t="n">
-        <v>0.630150264911862</v>
+        <v>0.545346249098718</v>
       </c>
       <c r="D10" t="n">
-        <v>0.675612087346519</v>
+        <v>0.55752688172043</v>
       </c>
       <c r="E10" t="n">
-        <v>0.717069414830609</v>
+        <v>0.507237386269644</v>
       </c>
       <c r="F10" t="n">
-        <v>0.640702263757202</v>
+        <v>0.678641251221896</v>
       </c>
       <c r="G10" t="n">
-        <v>0.424532572375503</v>
+        <v>0.353942652329749</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0538719219030896</v>
+        <v>0.0572643160790198</v>
       </c>
       <c r="I10" t="n">
-        <v>0.560561249054268</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1869,28 +3267,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.288113832601041</v>
+        <v>0.233355364648421</v>
       </c>
       <c r="D2" t="n">
-        <v>0.27903874517321</v>
+        <v>0.236807230475514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.269513580215516</v>
+        <v>0.216271108346652</v>
       </c>
       <c r="F2" t="n">
-        <v>0.546920984647097</v>
+        <v>0.233435362151603</v>
       </c>
       <c r="G2" t="n">
-        <v>0.572664272346927</v>
+        <v>0.223723983824703</v>
       </c>
       <c r="H2" t="n">
-        <v>0.399547223840348</v>
+        <v>0.330987735644165</v>
       </c>
       <c r="I2" t="n">
-        <v>0.200263182204939</v>
+        <v>0.107083571890185</v>
       </c>
       <c r="J2" t="n">
-        <v>0.248633374952977</v>
+        <v>0.137023098980483</v>
       </c>
     </row>
     <row r="3">
@@ -1898,31 +3296,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.288113832601041</v>
+        <v>0.233355364648421</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.667935209609999</v>
+        <v>0.575103267231468</v>
       </c>
       <c r="E3" t="n">
-        <v>0.692957791515257</v>
+        <v>0.525369019699554</v>
       </c>
       <c r="F3" t="n">
-        <v>0.545585790906465</v>
+        <v>0.698893276015059</v>
       </c>
       <c r="G3" t="n">
-        <v>0.59465605591079</v>
+        <v>0.657730682345629</v>
       </c>
       <c r="H3" t="n">
-        <v>0.447152061778061</v>
+        <v>0.325534429124834</v>
       </c>
       <c r="I3" t="n">
-        <v>0.451217011983314</v>
+        <v>0.286357954591708</v>
       </c>
       <c r="J3" t="n">
-        <v>0.682027460102886</v>
+        <v>0.490027317050492</v>
       </c>
     </row>
     <row r="4">
@@ -1930,31 +3328,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.27903874517321</v>
+        <v>0.236807230475514</v>
       </c>
       <c r="C4" t="n">
-        <v>0.667935209609999</v>
+        <v>0.575103267231468</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.720170836749734</v>
+        <v>0.588922760093157</v>
       </c>
       <c r="F4" t="n">
-        <v>0.512836617056298</v>
+        <v>0.546757563389031</v>
       </c>
       <c r="G4" t="n">
-        <v>0.549688424582829</v>
+        <v>0.567222831444898</v>
       </c>
       <c r="H4" t="n">
-        <v>0.414139771619706</v>
+        <v>0.241998217737488</v>
       </c>
       <c r="I4" t="n">
-        <v>0.248378870574247</v>
+        <v>0.116332302302512</v>
       </c>
       <c r="J4" t="n">
-        <v>0.848404345316451</v>
+        <v>0.675061239295518</v>
       </c>
     </row>
     <row r="5">
@@ -1962,31 +3360,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.269513580215516</v>
+        <v>0.216271108346652</v>
       </c>
       <c r="C5" t="n">
-        <v>0.692957791515257</v>
+        <v>0.525369019699554</v>
       </c>
       <c r="D5" t="n">
-        <v>0.720170836749734</v>
+        <v>0.588922760093157</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.568121842997124</v>
+        <v>0.717873154439542</v>
       </c>
       <c r="G5" t="n">
-        <v>0.540436541868002</v>
+        <v>0.520104594231091</v>
       </c>
       <c r="H5" t="n">
-        <v>0.410604830175679</v>
+        <v>0.286904850259504</v>
       </c>
       <c r="I5" t="n">
-        <v>0.406573791519463</v>
+        <v>0.358469750496591</v>
       </c>
       <c r="J5" t="n">
-        <v>0.770619846624554</v>
+        <v>0.552228380734329</v>
       </c>
     </row>
     <row r="6">
@@ -1994,31 +3392,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.546920984647097</v>
+        <v>0.233435362151603</v>
       </c>
       <c r="C6" t="n">
-        <v>0.545585790906465</v>
+        <v>0.698893276015059</v>
       </c>
       <c r="D6" t="n">
-        <v>0.512836617056298</v>
+        <v>0.546757563389031</v>
       </c>
       <c r="E6" t="n">
-        <v>0.568121842997124</v>
+        <v>0.717873154439542</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.700954353141441</v>
+        <v>0.678375309887973</v>
       </c>
       <c r="H6" t="n">
-        <v>0.554075787914723</v>
+        <v>0.309371136659384</v>
       </c>
       <c r="I6" t="n">
-        <v>0.320826402020681</v>
+        <v>0.418953459413488</v>
       </c>
       <c r="J6" t="n">
-        <v>0.503607612742547</v>
+        <v>0.515996272396106</v>
       </c>
     </row>
     <row r="7">
@@ -2026,31 +3424,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.572664272346927</v>
+        <v>0.223723983824703</v>
       </c>
       <c r="C7" t="n">
-        <v>0.59465605591079</v>
+        <v>0.657730682345629</v>
       </c>
       <c r="D7" t="n">
-        <v>0.549688424582829</v>
+        <v>0.567222831444898</v>
       </c>
       <c r="E7" t="n">
-        <v>0.540436541868002</v>
+        <v>0.520104594231091</v>
       </c>
       <c r="F7" t="n">
-        <v>0.700954353141441</v>
+        <v>0.678375309887973</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.657904997740206</v>
+        <v>0.381257219569525</v>
       </c>
       <c r="I7" t="n">
-        <v>0.224711206631003</v>
+        <v>0.169101612530764</v>
       </c>
       <c r="J7" t="n">
-        <v>0.505124841221251</v>
+        <v>0.435488393294371</v>
       </c>
     </row>
     <row r="8">
@@ -2058,31 +3456,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.399547223840348</v>
+        <v>0.330987735644165</v>
       </c>
       <c r="C8" t="n">
-        <v>0.447152061778061</v>
+        <v>0.325534429124834</v>
       </c>
       <c r="D8" t="n">
-        <v>0.414139771619706</v>
+        <v>0.241998217737488</v>
       </c>
       <c r="E8" t="n">
-        <v>0.410604830175679</v>
+        <v>0.286904850259504</v>
       </c>
       <c r="F8" t="n">
-        <v>0.554075787914723</v>
+        <v>0.309371136659384</v>
       </c>
       <c r="G8" t="n">
-        <v>0.657904997740206</v>
+        <v>0.381257219569525</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.155270923457497</v>
+        <v>0.0808553338647987</v>
       </c>
       <c r="J8" t="n">
-        <v>0.36853322590728</v>
+        <v>0.105958686310609</v>
       </c>
     </row>
     <row r="9">
@@ -2090,31 +3488,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.200263182204939</v>
+        <v>0.107083571890185</v>
       </c>
       <c r="C9" t="n">
-        <v>0.451217011983314</v>
+        <v>0.286357954591708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.248378870574247</v>
+        <v>0.116332302302512</v>
       </c>
       <c r="E9" t="n">
-        <v>0.406573791519463</v>
+        <v>0.358469750496591</v>
       </c>
       <c r="F9" t="n">
-        <v>0.320826402020681</v>
+        <v>0.418953459413488</v>
       </c>
       <c r="G9" t="n">
-        <v>0.224711206631003</v>
+        <v>0.169101612530764</v>
       </c>
       <c r="H9" t="n">
-        <v>0.155270923457497</v>
+        <v>0.0808553338647987</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.361105509385022</v>
+        <v>0.252622003271486</v>
       </c>
     </row>
     <row r="10">
@@ -2122,28 +3520,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.248633374952977</v>
+        <v>0.137023098980483</v>
       </c>
       <c r="C10" t="n">
-        <v>0.682027460102886</v>
+        <v>0.490027317050492</v>
       </c>
       <c r="D10" t="n">
-        <v>0.848404345316451</v>
+        <v>0.675061239295518</v>
       </c>
       <c r="E10" t="n">
-        <v>0.770619846624554</v>
+        <v>0.552228380734329</v>
       </c>
       <c r="F10" t="n">
-        <v>0.503607612742547</v>
+        <v>0.515996272396106</v>
       </c>
       <c r="G10" t="n">
-        <v>0.505124841221251</v>
+        <v>0.435488393294371</v>
       </c>
       <c r="H10" t="n">
-        <v>0.36853322590728</v>
+        <v>0.105958686310609</v>
       </c>
       <c r="I10" t="n">
-        <v>0.361105509385022</v>
+        <v>0.252622003271486</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -2200,28 +3598,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.397271306365073</v>
+        <v>0.350083816668734</v>
       </c>
       <c r="D2" t="n">
-        <v>0.153588410397621</v>
+        <v>0.16273141118296</v>
       </c>
       <c r="E2" t="n">
-        <v>0.36817300919797</v>
+        <v>0.267806527053129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.326850000840989</v>
+        <v>0.333959193184586</v>
       </c>
       <c r="G2" t="n">
-        <v>0.114082709853921</v>
+        <v>0.0742240950226942</v>
       </c>
       <c r="H2" t="n">
-        <v>0.334293934224994</v>
+        <v>0.335791237990014</v>
       </c>
       <c r="I2" t="n">
-        <v>0.399290644261623</v>
+        <v>0.344442976783761</v>
       </c>
       <c r="J2" t="n">
-        <v>0.428723464575154</v>
+        <v>0.377282163289082</v>
       </c>
     </row>
     <row r="3">
@@ -2229,31 +3627,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.397271306365073</v>
+        <v>0.350083816668734</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.448735612055422</v>
+        <v>0.566790727804098</v>
       </c>
       <c r="E3" t="n">
-        <v>0.713460592766963</v>
+        <v>0.594130861270243</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742711900952967</v>
+        <v>0.688369285491299</v>
       </c>
       <c r="G3" t="n">
-        <v>0.486075821865547</v>
+        <v>0.425458134690656</v>
       </c>
       <c r="H3" t="n">
-        <v>0.369094970088058</v>
+        <v>0.318691765394244</v>
       </c>
       <c r="I3" t="n">
-        <v>0.642490419785275</v>
+        <v>0.598787659913783</v>
       </c>
       <c r="J3" t="n">
-        <v>0.778504588697782</v>
+        <v>0.697623245981543</v>
       </c>
     </row>
     <row r="4">
@@ -2261,31 +3659,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.153588410397621</v>
+        <v>0.16273141118296</v>
       </c>
       <c r="C4" t="n">
-        <v>0.448735612055422</v>
+        <v>0.566790727804098</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.334211030317289</v>
+        <v>0.460186423324999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.420860172605848</v>
+        <v>0.429324248247203</v>
       </c>
       <c r="G4" t="n">
-        <v>0.600925106598839</v>
+        <v>0.772885573740358</v>
       </c>
       <c r="H4" t="n">
-        <v>0.121672415869355</v>
+        <v>0.135611020858302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.269097788448966</v>
+        <v>0.271810304167514</v>
       </c>
       <c r="J4" t="n">
-        <v>0.331489245975294</v>
+        <v>0.40501219820004</v>
       </c>
     </row>
     <row r="5">
@@ -2293,31 +3691,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.36817300919797</v>
+        <v>0.267806527053129</v>
       </c>
       <c r="C5" t="n">
-        <v>0.713460592766963</v>
+        <v>0.594130861270243</v>
       </c>
       <c r="D5" t="n">
-        <v>0.334211030317289</v>
+        <v>0.460186423324999</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.705532754294093</v>
+        <v>0.712088656175373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.336629826947949</v>
+        <v>0.319819296276916</v>
       </c>
       <c r="H5" t="n">
-        <v>0.386914588885593</v>
+        <v>0.262186779992744</v>
       </c>
       <c r="I5" t="n">
-        <v>0.636322626585745</v>
+        <v>0.54336946724676</v>
       </c>
       <c r="J5" t="n">
-        <v>0.805516256799526</v>
+        <v>0.697475674572348</v>
       </c>
     </row>
     <row r="6">
@@ -2325,31 +3723,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.326850000840989</v>
+        <v>0.333959193184586</v>
       </c>
       <c r="C6" t="n">
-        <v>0.742711900952967</v>
+        <v>0.688369285491299</v>
       </c>
       <c r="D6" t="n">
-        <v>0.420860172605848</v>
+        <v>0.429324248247203</v>
       </c>
       <c r="E6" t="n">
-        <v>0.705532754294093</v>
+        <v>0.712088656175373</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.498203525465896</v>
+        <v>0.313568574825813</v>
       </c>
       <c r="H6" t="n">
-        <v>0.348536918353287</v>
+        <v>0.439575420721625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.610730912861877</v>
+        <v>0.677498408229699</v>
       </c>
       <c r="J6" t="n">
-        <v>0.690674242586151</v>
+        <v>0.767933884301661</v>
       </c>
     </row>
     <row r="7">
@@ -2357,31 +3755,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.114082709853921</v>
+        <v>0.0742240950226942</v>
       </c>
       <c r="C7" t="n">
-        <v>0.486075821865547</v>
+        <v>0.425458134690656</v>
       </c>
       <c r="D7" t="n">
-        <v>0.600925106598839</v>
+        <v>0.772885573740358</v>
       </c>
       <c r="E7" t="n">
-        <v>0.336629826947949</v>
+        <v>0.319819296276916</v>
       </c>
       <c r="F7" t="n">
-        <v>0.498203525465896</v>
+        <v>0.313568574825813</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0733793731635017</v>
+        <v>0.0629655998947401</v>
       </c>
       <c r="I7" t="n">
-        <v>0.264913353790013</v>
+        <v>0.159530702146828</v>
       </c>
       <c r="J7" t="n">
-        <v>0.325224614695799</v>
+        <v>0.268509127868079</v>
       </c>
     </row>
     <row r="8">
@@ -2389,31 +3787,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.334293934224994</v>
+        <v>0.335791237990014</v>
       </c>
       <c r="C8" t="n">
-        <v>0.369094970088058</v>
+        <v>0.318691765394244</v>
       </c>
       <c r="D8" t="n">
-        <v>0.121672415869355</v>
+        <v>0.135611020858302</v>
       </c>
       <c r="E8" t="n">
-        <v>0.386914588885593</v>
+        <v>0.262186779992744</v>
       </c>
       <c r="F8" t="n">
-        <v>0.348536918353287</v>
+        <v>0.439575420721625</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0733793731635017</v>
+        <v>0.0629655998947401</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.529476059444332</v>
+        <v>0.508140110266071</v>
       </c>
       <c r="J8" t="n">
-        <v>0.487986769110646</v>
+        <v>0.397333289108783</v>
       </c>
     </row>
     <row r="9">
@@ -2421,31 +3819,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.399290644261623</v>
+        <v>0.344442976783761</v>
       </c>
       <c r="C9" t="n">
-        <v>0.642490419785275</v>
+        <v>0.598787659913783</v>
       </c>
       <c r="D9" t="n">
-        <v>0.269097788448966</v>
+        <v>0.271810304167514</v>
       </c>
       <c r="E9" t="n">
-        <v>0.636322626585745</v>
+        <v>0.54336946724676</v>
       </c>
       <c r="F9" t="n">
-        <v>0.610730912861877</v>
+        <v>0.677498408229699</v>
       </c>
       <c r="G9" t="n">
-        <v>0.264913353790013</v>
+        <v>0.159530702146828</v>
       </c>
       <c r="H9" t="n">
-        <v>0.529476059444332</v>
+        <v>0.508140110266071</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.81311026782323</v>
+        <v>0.731547704981901</v>
       </c>
     </row>
     <row r="10">
@@ -2453,28 +3851,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.428723464575154</v>
+        <v>0.377282163289082</v>
       </c>
       <c r="C10" t="n">
-        <v>0.778504588697782</v>
+        <v>0.697623245981543</v>
       </c>
       <c r="D10" t="n">
-        <v>0.331489245975294</v>
+        <v>0.40501219820004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.805516256799526</v>
+        <v>0.697475674572348</v>
       </c>
       <c r="F10" t="n">
-        <v>0.690674242586151</v>
+        <v>0.767933884301661</v>
       </c>
       <c r="G10" t="n">
-        <v>0.325224614695799</v>
+        <v>0.268509127868079</v>
       </c>
       <c r="H10" t="n">
-        <v>0.487986769110646</v>
+        <v>0.397333289108783</v>
       </c>
       <c r="I10" t="n">
-        <v>0.81311026782323</v>
+        <v>0.731547704981901</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -2531,28 +3929,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.184474625587931</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002</v>
+        <v>0.225264605599194</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.27092405478135</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.179939944664695</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.157104664356787</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.319067792032221</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.299427401890363</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.132441882339348</v>
       </c>
     </row>
     <row r="3">
@@ -2560,31 +3958,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.184474625587931</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.314454037821994</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.516134923756252</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.803461930790523</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.188799801974201</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.437964389848749</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.332339131707739</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.676337013714967</v>
       </c>
     </row>
     <row r="4">
@@ -2592,31 +3990,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002</v>
+        <v>0.225264605599194</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.314454037821994</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004</v>
+        <v>0.459999289828664</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001</v>
+        <v>0.248310015543815</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002</v>
+        <v>0.730314262625748</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.234316583281522</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001</v>
+        <v>0.265447806931858</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.160000090336848</v>
       </c>
     </row>
     <row r="5">
@@ -2624,31 +4022,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.27092405478135</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.516134923756252</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004</v>
+        <v>0.459999289828664</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.012</v>
+        <v>0.525131946346997</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.303079609786315</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.585509559809942</v>
       </c>
       <c r="I5" t="n">
-        <v>0.042</v>
+        <v>0.384715049217255</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.357615521514747</v>
       </c>
     </row>
     <row r="6">
@@ -2656,31 +4054,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.179939944664695</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.803461930790523</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001</v>
+        <v>0.248310015543815</v>
       </c>
       <c r="E6" t="n">
-        <v>0.012</v>
+        <v>0.525131946346997</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.129316017605598</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.467822647179166</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007</v>
+        <v>0.293591611421296</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.624149634130847</v>
       </c>
     </row>
     <row r="7">
@@ -2688,31 +4086,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.157104664356787</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.188799801974201</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002</v>
+        <v>0.730314262625748</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.303079609786315</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.129316017605598</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.0823490305535473</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.121663727968376</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.0447442357517615</v>
       </c>
     </row>
     <row r="8">
@@ -2720,31 +4118,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.319067792032221</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.437964389848749</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.234316583281522</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.585509559809942</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.467822647179166</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.0823490305535473</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.607785960473745</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.542219100989854</v>
       </c>
     </row>
     <row r="9">
@@ -2752,31 +4150,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.299427401890363</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.332339131707739</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001</v>
+        <v>0.265447806931858</v>
       </c>
       <c r="E9" t="n">
-        <v>0.042</v>
+        <v>0.384715049217255</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007</v>
+        <v>0.293591611421296</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.121663727968376</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.607785960473745</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.47355081726303</v>
       </c>
     </row>
     <row r="10">
@@ -2784,28 +4182,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.132441882339348</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.676337013714967</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.160000090336848</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.357615521514747</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.624149634130847</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.0447442357517615</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.542219100989854</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.47355081726303</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -2862,28 +4260,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.184474625587931</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.225264605599193</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.270924054781349</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.179939944664694</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.157104664356787</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.319067792032221</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.299427401890363</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.132441882339348</v>
       </c>
     </row>
     <row r="3">
@@ -2891,31 +4289,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.184474625587931</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.011</v>
+        <v>0.314454037821993</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001</v>
+        <v>0.516134923756252</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.803461930790524</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.188799801974201</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.437964389848748</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.332339131707738</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.676337013714967</v>
       </c>
     </row>
     <row r="4">
@@ -2923,31 +4321,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.225264605599193</v>
       </c>
       <c r="C4" t="n">
-        <v>0.011</v>
+        <v>0.314454037821993</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09</v>
+        <v>0.459999289828663</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005</v>
+        <v>0.248310015543815</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.730314262625749</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.234316583281522</v>
       </c>
       <c r="I4" t="n">
-        <v>0.192</v>
+        <v>0.265447806931858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.017</v>
+        <v>0.160000090336847</v>
       </c>
     </row>
     <row r="5">
@@ -2955,31 +4353,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.270924054781349</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001</v>
+        <v>0.516134923756252</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09</v>
+        <v>0.459999289828663</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.38</v>
+        <v>0.525131946346998</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.303079609786315</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.585509559809942</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003</v>
+        <v>0.384715049217254</v>
       </c>
       <c r="J5" t="n">
-        <v>0.023</v>
+        <v>0.357615521514747</v>
       </c>
     </row>
     <row r="6">
@@ -2987,31 +4385,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.179939944664694</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.803461930790524</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005</v>
+        <v>0.248310015543815</v>
       </c>
       <c r="E6" t="n">
-        <v>0.38</v>
+        <v>0.525131946346998</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.129316017605598</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.467822647179166</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.293591611421296</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.624149634130847</v>
       </c>
     </row>
     <row r="7">
@@ -3019,31 +4417,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.157104664356787</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.188799801974201</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.730314262625749</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.303079609786315</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.129316017605598</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.0823490305535472</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.121663727968375</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.0447442357517615</v>
       </c>
     </row>
     <row r="8">
@@ -3051,31 +4449,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.319067792032221</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.437964389848748</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.234316583281522</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.585509559809942</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.467822647179166</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.0823490305535472</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.607785960473744</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.542219100989854</v>
       </c>
     </row>
     <row r="9">
@@ -3083,31 +4481,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.299427401890363</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.332339131707738</v>
       </c>
       <c r="D9" t="n">
-        <v>0.192</v>
+        <v>0.265447806931858</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003</v>
+        <v>0.384715049217254</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.293591611421296</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.121663727968375</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.607785960473744</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.47355081726303</v>
       </c>
     </row>
     <row r="10">
@@ -3115,28 +4513,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.132441882339348</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.676337013714967</v>
       </c>
       <c r="D10" t="n">
-        <v>0.017</v>
+        <v>0.160000090336847</v>
       </c>
       <c r="E10" t="n">
-        <v>0.023</v>
+        <v>0.357615521514747</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.624149634130847</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.0447442357517615</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.542219100989854</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.47355081726303</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -3196,10 +4594,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -3211,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -3228,22 +4626,22 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -3254,31 +4652,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.033</v>
+        <v>0.011</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J4" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3286,31 +4684,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D5" t="n">
-        <v>0.033</v>
+        <v>0.011</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3321,13 +4719,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -3336,13 +4734,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="7">
@@ -3356,7 +4754,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3371,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3391,10 +4789,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -3403,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3414,31 +4812,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="10">
@@ -3452,13 +4850,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3467,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -3539,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3559,13 +4957,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3574,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -3588,16 +4986,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3606,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3623,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3641,7 +5039,7 @@
         <v>0.003</v>
       </c>
       <c r="J5" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3652,13 +5050,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -3670,10 +5068,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
@@ -3713,7 +5111,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -3748,16 +5146,16 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E9" t="n">
         <v>0.003</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -3769,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3786,10 +5184,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3798,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -3855,28 +5253,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.283836695730393</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.273698311765096</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.330598811954358</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.337326386635623</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.278772075018246</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.50334976020945</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.293702666886766</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.222360509720814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3884,31 +5282,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.283836695730393</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.529672323930121</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.639814386647353</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.647496017617973</v>
+        <v>0.01</v>
       </c>
       <c r="G3" t="n">
-        <v>0.414915673551531</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.367961207374274</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.544914834775839</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.672180165849578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3916,31 +5314,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.273698311765096</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.529672323930121</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.55097974107565</v>
+        <v>0.005</v>
       </c>
       <c r="F4" t="n">
-        <v>0.47890665486492</v>
+        <v>0.003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.577670726128128</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.22546181538952</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.392481002406655</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.504220935848044</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="5">
@@ -3948,31 +5346,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.330598811954358</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.639814386647353</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.55097974107565</v>
+        <v>0.005</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.697602659318281</v>
+        <v>0.135</v>
       </c>
       <c r="G5" t="n">
-        <v>0.41545581032406</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.349990193421606</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.574607783929672</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.667198741495714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3980,31 +5378,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.337326386635623</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.647496017617973</v>
+        <v>0.01</v>
       </c>
       <c r="D6" t="n">
-        <v>0.47890665486492</v>
+        <v>0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.697602659318281</v>
+        <v>0.135</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.517302354267642</v>
+        <v>0.004</v>
       </c>
       <c r="H6" t="n">
-        <v>0.351329040914123</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.493520138069671</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.563326782866544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4012,31 +5410,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.278772075018246</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.414915673551531</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.577670726128128</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.41545581032406</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.517302354267642</v>
+        <v>0.004</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.230616769024429</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.261049676425436</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.324526345269029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4044,31 +5442,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.50334976020945</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.367961207374274</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.22546181538952</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.349990193421606</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.351329040914123</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.230616769024429</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.353959188519603</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.405291567270804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4076,31 +5474,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.293702666886766</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.544914834775839</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.392481002406655</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.574607783929672</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.493520138069671</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.261049676425436</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.353959188519603</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.556484676655344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4108,28 +5506,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.222360509720814</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.672180165849578</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.504220935848044</v>
+        <v>0.003</v>
       </c>
       <c r="E10" t="n">
-        <v>0.667198741495714</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.563326782866544</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.324526345269029</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.405291567270804</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.556484676655344</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
